--- a/fixtures/xlsx/loan.xlsx
+++ b/fixtures/xlsx/loan.xlsx
@@ -235,7 +235,7 @@
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">VLOOKUP(B3,A6:C9,2,TRUE())</f>
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
